--- a/EXCEL/class notes/day9 date conditional/Adv filter.xlsx
+++ b/EXCEL/class notes/day9 date conditional/Adv filter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day9 date conditional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A49ECB-1634-45DF-BB0B-91886EC2B68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0255A7BC-D8CE-4A06-B3DC-3D6C9B402CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{FA35C046-231F-4768-9E66-2D339F927638}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{FA35C046-231F-4768-9E66-2D339F927638}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -744,14 +753,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E9ABF4-ED36-425D-8654-D77523E0EB5A}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -771,7 +780,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -791,7 +800,7 @@
       </c>
       <c r="F2" s="1">
         <f ca="1">TODAY()</f>
-        <v>45569</v>
+        <v>45925</v>
       </c>
       <c r="I2" s="17">
         <v>0</v>
@@ -800,7 +809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -820,7 +829,7 @@
       </c>
       <c r="F3" s="1">
         <f t="shared" ref="F3:F11" ca="1" si="2">TODAY()</f>
-        <v>45569</v>
+        <v>45925</v>
       </c>
       <c r="I3" s="17">
         <v>35</v>
@@ -829,7 +838,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -849,7 +858,7 @@
       </c>
       <c r="F4" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>45569</v>
+        <v>45925</v>
       </c>
       <c r="I4" s="17">
         <v>60</v>
@@ -858,7 +867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -878,7 +887,7 @@
       </c>
       <c r="F5" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>45569</v>
+        <v>45925</v>
       </c>
       <c r="I5" s="17">
         <v>75</v>
@@ -887,7 +896,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -907,10 +916,10 @@
       </c>
       <c r="F6" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>45569</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -930,10 +939,10 @@
       </c>
       <c r="F7" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>45569</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -953,10 +962,10 @@
       </c>
       <c r="F8" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>45569</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -976,10 +985,10 @@
       </c>
       <c r="F9" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>45569</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -999,10 +1008,10 @@
       </c>
       <c r="F10" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>45569</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1010</v>
       </c>
@@ -1022,10 +1031,10 @@
       </c>
       <c r="F11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>45569</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1001</v>
       </c>
@@ -1045,10 +1054,10 @@
       </c>
       <c r="F12" s="3">
         <f ca="1">F2-1</f>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>1002</v>
       </c>
@@ -1068,10 +1077,10 @@
       </c>
       <c r="F13" s="3">
         <f t="shared" ref="F13:F31" ca="1" si="3">F3-1</f>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>1003</v>
       </c>
@@ -1091,10 +1100,10 @@
       </c>
       <c r="F14" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>1004</v>
       </c>
@@ -1114,10 +1123,10 @@
       </c>
       <c r="F15" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>1005</v>
       </c>
@@ -1137,10 +1146,10 @@
       </c>
       <c r="F16" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>1006</v>
       </c>
@@ -1160,10 +1169,10 @@
       </c>
       <c r="F17" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>1007</v>
       </c>
@@ -1183,10 +1192,10 @@
       </c>
       <c r="F18" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1008</v>
       </c>
@@ -1206,10 +1215,10 @@
       </c>
       <c r="F19" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>1009</v>
       </c>
@@ -1229,10 +1238,10 @@
       </c>
       <c r="F20" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>1010</v>
       </c>
@@ -1252,10 +1261,10 @@
       </c>
       <c r="F21" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>45568</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1275,10 +1284,10 @@
       </c>
       <c r="F22" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1002</v>
       </c>
@@ -1298,10 +1307,10 @@
       </c>
       <c r="F23" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1003</v>
       </c>
@@ -1321,10 +1330,10 @@
       </c>
       <c r="F24" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1004</v>
       </c>
@@ -1344,10 +1353,10 @@
       </c>
       <c r="F25" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1005</v>
       </c>
@@ -1367,10 +1376,10 @@
       </c>
       <c r="F26" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1006</v>
       </c>
@@ -1390,10 +1399,10 @@
       </c>
       <c r="F27" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1007</v>
       </c>
@@ -1413,10 +1422,10 @@
       </c>
       <c r="F28" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1008</v>
       </c>
@@ -1436,10 +1445,10 @@
       </c>
       <c r="F29" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1009</v>
       </c>
@@ -1459,10 +1468,10 @@
       </c>
       <c r="F30" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1010</v>
       </c>
@@ -1482,7 +1491,7 @@
       </c>
       <c r="F31" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>45567</v>
+        <v>45923</v>
       </c>
     </row>
   </sheetData>
@@ -1503,14 +1512,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{215BC50D-BE28-4441-BA76-4B316C826FD5}">
   <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1545,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1002</v>
       </c>
@@ -1562,7 +1571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -1591,7 +1600,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1010</v>
       </c>
@@ -1620,7 +1629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -1646,7 +1655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1009</v>
       </c>
@@ -1666,7 +1675,7 @@
         <v>45217</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1001</v>
       </c>
@@ -1686,7 +1695,7 @@
         <v>45217</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>1005</v>
       </c>
@@ -1706,7 +1715,7 @@
         <v>45217</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1008</v>
       </c>
@@ -1730,7 +1739,7 @@
       </c>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1003</v>
       </c>
@@ -1750,7 +1759,7 @@
         <v>45218</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1006</v>
       </c>
@@ -1773,7 +1782,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1005</v>
       </c>
@@ -1798,7 +1807,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1006</v>
       </c>
@@ -1824,7 +1833,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>1007</v>
       </c>
@@ -1856,7 +1865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>1003</v>
       </c>
@@ -1888,7 +1897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1004</v>
       </c>
@@ -1920,7 +1929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1005</v>
       </c>
@@ -1952,7 +1961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1007</v>
       </c>
@@ -1972,7 +1981,7 @@
         <v>45218</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1010</v>
       </c>
@@ -1992,7 +2001,7 @@
         <v>45217</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1002</v>
       </c>
@@ -2012,7 +2021,7 @@
         <v>45218</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1009</v>
       </c>
@@ -2032,7 +2041,7 @@
         <v>45218</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1009</v>
       </c>
@@ -2052,7 +2061,7 @@
         <v>45216</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1003</v>
       </c>
@@ -2072,7 +2081,7 @@
         <v>45216</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1007</v>
       </c>
@@ -2092,7 +2101,7 @@
         <v>45216</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1008</v>
       </c>
@@ -2112,7 +2121,7 @@
         <v>45216</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>1006</v>
       </c>
@@ -2132,7 +2141,7 @@
         <v>45217</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>1004</v>
       </c>
@@ -2152,7 +2161,7 @@
         <v>45217</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>1002</v>
       </c>
@@ -2172,7 +2181,7 @@
         <v>45217</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1001</v>
       </c>
@@ -2192,7 +2201,7 @@
         <v>45218</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1010</v>
       </c>
@@ -2212,7 +2221,7 @@
         <v>45218</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1008</v>
       </c>
@@ -2253,14 +2262,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5CB75E9-84D6-4C25-A8C5-343192260E12}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2289,7 +2298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -2318,7 +2327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -2350,7 +2359,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -2382,7 +2391,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -2411,7 +2420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -2434,7 +2443,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -2457,7 +2466,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -2480,7 +2489,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -2507,7 +2516,7 @@
       </c>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -2530,7 +2539,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1010</v>
       </c>
@@ -2556,7 +2565,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1001</v>
       </c>
@@ -2584,7 +2593,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>1002</v>
       </c>
@@ -2613,7 +2622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>1003</v>
       </c>
@@ -2648,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>1004</v>
       </c>
@@ -2683,7 +2692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>1005</v>
       </c>
@@ -2718,7 +2727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>1006</v>
       </c>
@@ -2753,7 +2762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>1007</v>
       </c>
@@ -2776,7 +2785,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1008</v>
       </c>
@@ -2799,7 +2808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>1009</v>
       </c>
@@ -2822,7 +2831,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>1010</v>
       </c>
@@ -2845,7 +2854,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -2868,7 +2877,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1002</v>
       </c>
@@ -2891,7 +2900,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1003</v>
       </c>
@@ -2914,7 +2923,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1004</v>
       </c>
@@ -2937,7 +2946,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1005</v>
       </c>
@@ -2960,7 +2969,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1006</v>
       </c>
@@ -2983,7 +2992,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1007</v>
       </c>
@@ -3006,7 +3015,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1008</v>
       </c>
@@ -3029,7 +3038,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1009</v>
       </c>
@@ -3052,7 +3061,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1010</v>
       </c>
@@ -3075,7 +3084,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>1001</v>
       </c>
@@ -3098,7 +3107,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>1002</v>
       </c>
@@ -3121,7 +3130,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>1003</v>
       </c>
@@ -3144,7 +3153,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>1004</v>
       </c>
@@ -3167,7 +3176,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>1005</v>
       </c>
@@ -3190,7 +3199,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>1006</v>
       </c>
@@ -3213,7 +3222,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>1007</v>
       </c>
@@ -3236,7 +3245,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>1008</v>
       </c>
@@ -3259,7 +3268,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>1009</v>
       </c>
@@ -3282,7 +3291,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>1010</v>
       </c>
@@ -3315,7 +3324,7 @@
     <sortCondition ref="O14:O17"/>
   </sortState>
   <conditionalFormatting sqref="G2:G21 E2:E41">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"First class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3326,19 +3335,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DDED0AF-E0B7-4775-B12D-D9BA740CC65F}">
   <dimension ref="A1:N31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="21" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="21" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" style="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" customWidth="1"/>
+    <col min="15" max="15" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3364,7 +3374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1002</v>
       </c>
@@ -3393,7 +3403,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>1004</v>
       </c>
@@ -3416,7 +3426,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>1006</v>
       </c>
@@ -3439,7 +3449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>1010</v>
       </c>
@@ -3477,7 +3487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>1003</v>
       </c>
@@ -3515,7 +3525,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>1007</v>
       </c>
@@ -3553,7 +3563,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>1001</v>
       </c>
@@ -3591,7 +3601,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>1005</v>
       </c>
@@ -3629,7 +3639,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>1008</v>
       </c>
@@ -3649,7 +3659,7 @@
         <v>45569</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>1009</v>
       </c>
@@ -3669,7 +3679,7 @@
         <v>45569</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>1003</v>
       </c>
@@ -3707,7 +3717,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1007</v>
       </c>
@@ -3745,7 +3755,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>1008</v>
       </c>
@@ -3783,7 +3793,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>1009</v>
       </c>
@@ -3821,7 +3831,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>1005</v>
       </c>
@@ -3859,7 +3869,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>1006</v>
       </c>
@@ -3897,7 +3907,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>1001</v>
       </c>
@@ -3935,7 +3945,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>1002</v>
       </c>
@@ -3955,7 +3965,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1004</v>
       </c>
@@ -3975,7 +3985,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>1010</v>
       </c>
@@ -3995,7 +4005,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>1001</v>
       </c>
@@ -4015,7 +4025,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>1008</v>
       </c>
@@ -4035,7 +4045,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>1010</v>
       </c>
@@ -4055,7 +4065,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>1002</v>
       </c>
@@ -4075,7 +4085,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>1009</v>
       </c>
@@ -4095,7 +4105,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>1004</v>
       </c>
@@ -4115,7 +4125,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>1005</v>
       </c>
@@ -4135,7 +4145,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>1007</v>
       </c>
@@ -4155,7 +4165,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>1003</v>
       </c>
@@ -4175,7 +4185,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>1006</v>
       </c>
@@ -4197,7 +4207,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E31">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"First class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4208,14 +4218,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21A40E1-8AB6-430A-AD48-C40E9C60E926}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -4238,7 +4248,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1002</v>
       </c>
@@ -4261,7 +4271,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>1004</v>
       </c>
@@ -4284,7 +4294,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>1006</v>
       </c>
@@ -4307,7 +4317,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1003</v>
       </c>
@@ -4330,7 +4340,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1007</v>
       </c>
@@ -4353,7 +4363,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>1008</v>
       </c>
@@ -4376,7 +4386,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1009</v>
       </c>
@@ -4399,7 +4409,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1001</v>
       </c>
@@ -4422,7 +4432,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>1008</v>
       </c>
@@ -4445,7 +4455,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>1010</v>
       </c>
@@ -4468,7 +4478,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>1001</v>
       </c>
@@ -4491,7 +4501,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>1005</v>
       </c>
@@ -4514,7 +4524,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>1008</v>
       </c>
@@ -4537,7 +4547,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>1009</v>
       </c>
@@ -4560,7 +4570,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>1001</v>
       </c>
@@ -4583,7 +4593,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>1002</v>
       </c>
@@ -4606,7 +4616,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>1004</v>
       </c>
@@ -4629,7 +4639,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>1010</v>
       </c>
@@ -4652,7 +4662,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1003</v>
       </c>
@@ -4675,7 +4685,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>1006</v>
       </c>
@@ -4698,7 +4708,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>1010</v>
       </c>
@@ -4721,7 +4731,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>1002</v>
       </c>
@@ -4744,7 +4754,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>1009</v>
       </c>
@@ -4767,7 +4777,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>1003</v>
       </c>
@@ -4790,7 +4800,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>1007</v>
       </c>
@@ -4813,7 +4823,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>1005</v>
       </c>
@@ -4836,7 +4846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>1006</v>
       </c>
@@ -4859,7 +4869,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>1004</v>
       </c>
@@ -4882,7 +4892,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>1005</v>
       </c>
@@ -4905,7 +4915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>1007</v>
       </c>
@@ -4935,7 +4945,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="G2 E2:E31">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"First class"</formula>
     </cfRule>
   </conditionalFormatting>
